--- a/Excel/WeaponConfig.xlsx
+++ b/Excel/WeaponConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="54">
   <si>
     <t>#</t>
   </si>
@@ -49,16 +49,22 @@
     <t>Name</t>
   </si>
   <si>
-    <t>AttrIdList</t>
-  </si>
-  <si>
-    <t>AttrValueList</t>
-  </si>
-  <si>
-    <t>SpeAtrId</t>
-  </si>
-  <si>
-    <t>SpeAtrVue</t>
+    <t>Logo</t>
+  </si>
+  <si>
+    <t>AtrIdList</t>
+  </si>
+  <si>
+    <t>AtrVueList</t>
+  </si>
+  <si>
+    <t>GradeAtrIdList</t>
+  </si>
+  <si>
+    <t>GradeAtrVueList</t>
+  </si>
+  <si>
+    <t>Des</t>
   </si>
   <si>
     <t>Id</t>
@@ -73,7 +79,10 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>丈八蛇矛</t>
+    <t>惊鸿剑</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_1</t>
   </si>
   <si>
     <t>1,2,3</t>
@@ -82,37 +91,58 @@
     <t>2000,200,200</t>
   </si>
   <si>
+    <t>1001,2001</t>
+  </si>
+  <si>
+    <t>6,1</t>
+  </si>
+  <si>
     <t>血量</t>
   </si>
   <si>
-    <t>等级40级</t>
-  </si>
-  <si>
-    <t>青龙偃月</t>
+    <t>等级{0}级</t>
+  </si>
+  <si>
+    <t>天蚕甲</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_2</t>
   </si>
   <si>
     <t>3000,300,300</t>
   </si>
   <si>
+    <t>1002,2002</t>
+  </si>
+  <si>
     <t>防御</t>
   </si>
   <si>
-    <t>看广告300个</t>
-  </si>
-  <si>
-    <t>方天画戟</t>
+    <t>看广告{0}个</t>
+  </si>
+  <si>
+    <t>归元佩</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_3</t>
   </si>
   <si>
     <t>4000,400,400</t>
   </si>
   <si>
+    <t>1003,2003</t>
+  </si>
+  <si>
     <t>攻击</t>
   </si>
   <si>
-    <t>登录10天</t>
-  </si>
-  <si>
-    <t>龙胆枪</t>
+    <t>登录{0}天</t>
+  </si>
+  <si>
+    <t>追风剑</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_4</t>
   </si>
   <si>
     <t>5000,500,500</t>
@@ -124,7 +154,10 @@
     <t>专属</t>
   </si>
   <si>
-    <t>诸葛连弩</t>
+    <t>疾风弩</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_5</t>
   </si>
   <si>
     <t>6000,600,600</t>
@@ -133,7 +166,10 @@
     <t>攻速</t>
   </si>
   <si>
-    <t>麒麟弓</t>
+    <t>追魂刺</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_6</t>
   </si>
   <si>
     <t>7000,700,700</t>
@@ -145,7 +181,10 @@
     <t>技能总等级300级</t>
   </si>
   <si>
-    <t>钩镰枪</t>
+    <t>夺命枪</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_7</t>
   </si>
   <si>
     <t>8000,800,800</t>
@@ -167,7 +206,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -191,6 +230,12 @@
     <font>
       <sz val="9"/>
       <color rgb="FF05073B"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -663,137 +708,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -801,6 +846,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1121,7 +1170,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XEO19"/>
+  <dimension ref="A1:XEP19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1129,40 +1178,35 @@
     <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.25" style="2" customWidth="1"/>
-    <col min="9" max="10" width="20.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.4166666666667" style="2" customWidth="1"/>
-    <col min="12" max="12" width="14.25" style="2" customWidth="1"/>
-    <col min="13" max="16361" width="9" style="2"/>
-    <col min="16362" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="18.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.25" style="2" customWidth="1"/>
+    <col min="10" max="11" width="20.5" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12.4166666666667" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.25" style="2" customWidth="1"/>
+    <col min="14" max="16362" width="9" style="2"/>
+    <col min="16363" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12 16362:16369">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="K1" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="I1" s="2"/>
       <c r="L1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12 16362:16369">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="K2" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="I2" s="2"/>
       <c r="L2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12 16362:16369">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1189,12 +1233,18 @@
       <c r="J3" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:12 16362:16369">
+      <c r="K3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -1217,36 +1267,48 @@
       <c r="J4" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12 16362:16369">
+      <c r="K4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:12 16362:16369">
+        <v>14</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1257,28 +1319,31 @@
         <v>40</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="1">
-        <v>1001</v>
-      </c>
-      <c r="J6" s="1">
-        <v>6</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="H6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="L6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:12 16362:16369">
+        <v>21</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1286,31 +1351,34 @@
         <v>2</v>
       </c>
       <c r="E7" s="1">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1002</v>
-      </c>
-      <c r="J7" s="1">
-        <v>6</v>
-      </c>
-      <c r="K7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:12 16362:16369">
+        <v>27</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1320,29 +1388,38 @@
       <c r="E8" s="1">
         <v>10</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1003</v>
-      </c>
-      <c r="J8" s="1">
-        <v>6</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>24</v>
+      <c r="F8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:12 16362:16369">
+        <v>33</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1352,29 +1429,38 @@
       <c r="E9" s="1">
         <v>107</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="1">
+      <c r="F9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="1">
         <v>10</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>1</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="L9" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:12 16362:16369">
+        <v>38</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1384,29 +1470,38 @@
       <c r="E10" s="1">
         <v>108</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="1">
+      <c r="F10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="1">
         <v>11</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>1</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="L10" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:12 16362:16369">
+        <v>43</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1416,28 +1511,30 @@
       <c r="E11" s="1">
         <v>300</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="1">
+      <c r="F11" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="1">
         <v>21</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>1</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="XEH11" s="1"/>
+      <c r="L11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="XEI11" s="1"/>
       <c r="XEJ11" s="1"/>
       <c r="XEK11" s="1"/>
@@ -1445,8 +1542,15 @@
       <c r="XEM11" s="1"/>
       <c r="XEN11" s="1"/>
       <c r="XEO11" s="1"/>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:12 16362:16369">
+      <c r="XEP11" s="1"/>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+      <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1457,27 +1561,29 @@
         <v>36</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="I12" s="1">
+        <v>49</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" s="1">
         <v>22</v>
       </c>
-      <c r="J12" s="1">
+      <c r="K12" s="1">
         <v>5</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="L12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="XEH12" s="1"/>
+        <v>52</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="XEI12" s="1"/>
       <c r="XEJ12" s="1"/>
       <c r="XEK12" s="1"/>
@@ -1485,17 +1591,18 @@
       <c r="XEM12" s="1"/>
       <c r="XEN12" s="1"/>
       <c r="XEO12" s="1"/>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:12 16362:16369">
+      <c r="XEP12" s="1"/>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:13 16363:16370">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="1"/>
+      <c r="G13" s="4"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
-      <c r="XEH13" s="1"/>
+      <c r="K13" s="1"/>
       <c r="XEI13" s="1"/>
       <c r="XEJ13" s="1"/>
       <c r="XEK13" s="1"/>
@@ -1503,17 +1610,18 @@
       <c r="XEM13" s="1"/>
       <c r="XEN13" s="1"/>
       <c r="XEO13" s="1"/>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:12 16362:16369">
+      <c r="XEP13" s="1"/>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:13 16363:16370">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="1"/>
+      <c r="G14" s="4"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
-      <c r="XEH14" s="1"/>
+      <c r="K14" s="1"/>
       <c r="XEI14" s="1"/>
       <c r="XEJ14" s="1"/>
       <c r="XEK14" s="1"/>
@@ -1521,17 +1629,18 @@
       <c r="XEM14" s="1"/>
       <c r="XEN14" s="1"/>
       <c r="XEO14" s="1"/>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:12 16362:16369">
+      <c r="XEP14" s="1"/>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:13 16363:16370">
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="4"/>
-      <c r="G15" s="1"/>
+      <c r="G15" s="4"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
-      <c r="XEH15" s="1"/>
+      <c r="K15" s="1"/>
       <c r="XEI15" s="1"/>
       <c r="XEJ15" s="1"/>
       <c r="XEK15" s="1"/>
@@ -1539,38 +1648,43 @@
       <c r="XEM15" s="1"/>
       <c r="XEN15" s="1"/>
       <c r="XEO15" s="1"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:12 16362:16369">
+      <c r="XEP15" s="1"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:13 16363:16370">
       <c r="F16" s="4"/>
-      <c r="G16" s="1"/>
+      <c r="G16" s="4"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
-    </row>
-    <row r="17" customHeight="1" spans="6:10">
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" customHeight="1" spans="6:11">
       <c r="F17" s="4"/>
-      <c r="G17" s="1"/>
+      <c r="G17" s="4"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
-    </row>
-    <row r="18" customHeight="1" spans="6:10">
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" customHeight="1" spans="6:11">
       <c r="F18" s="4"/>
-      <c r="G18" s="1"/>
+      <c r="G18" s="4"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
-    </row>
-    <row r="19" customHeight="1" spans="6:10">
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" customHeight="1" spans="6:11">
       <c r="F19" s="4"/>
-      <c r="G19" s="1"/>
+      <c r="G19" s="4"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="J3 J4 E5:G5 H5 I5 J5 I3:I4 C3:D5 E3:H4" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:K3 C4:I4 J4 K4 C5:I5 J5 K5 M3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/WeaponConfig.xlsx
+++ b/Excel/WeaponConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="56">
   <si>
     <t>#</t>
   </si>
@@ -64,6 +64,12 @@
     <t>GradeAtrVueList</t>
   </si>
   <si>
+    <t>Fee</t>
+  </si>
+  <si>
+    <t>Exp</t>
+  </si>
+  <si>
     <t>Des</t>
   </si>
   <si>
@@ -79,88 +85,88 @@
     <t>int[]</t>
   </si>
   <si>
+    <t>归元佩</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_3</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
+    <t>1000,100,100</t>
+  </si>
+  <si>
+    <t>1001,2001</t>
+  </si>
+  <si>
+    <t>6,1</t>
+  </si>
+  <si>
+    <t>血量</t>
+  </si>
+  <si>
+    <t>等级{0}级</t>
+  </si>
+  <si>
+    <t>天蚕甲</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_2</t>
+  </si>
+  <si>
+    <t>1500,150,150</t>
+  </si>
+  <si>
+    <t>1002,2002</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>看广告{0}个</t>
+  </si>
+  <si>
     <t>惊鸿剑</t>
   </si>
   <si>
     <t>Bag/Equip/Box_Equip_1_1</t>
   </si>
   <si>
-    <t>1,2,3</t>
-  </si>
-  <si>
     <t>2000,200,200</t>
   </si>
   <si>
-    <t>1001,2001</t>
-  </si>
-  <si>
-    <t>6,1</t>
-  </si>
-  <si>
-    <t>血量</t>
-  </si>
-  <si>
-    <t>等级{0}级</t>
-  </si>
-  <si>
-    <t>天蚕甲</t>
-  </si>
-  <si>
-    <t>Bag/Equip/Box_Equip_1_2</t>
+    <t>1003,2003</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>登录{0}天</t>
+  </si>
+  <si>
+    <t>追风剑</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_4</t>
   </si>
   <si>
     <t>3000,300,300</t>
   </si>
   <si>
-    <t>1002,2002</t>
-  </si>
-  <si>
-    <t>防御</t>
-  </si>
-  <si>
-    <t>看广告{0}个</t>
-  </si>
-  <si>
-    <t>归元佩</t>
-  </si>
-  <si>
-    <t>Bag/Equip/Box_Equip_1_3</t>
+    <t>cd</t>
+  </si>
+  <si>
+    <t>专属</t>
+  </si>
+  <si>
+    <t>疾风弩</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_5</t>
   </si>
   <si>
     <t>4000,400,400</t>
-  </si>
-  <si>
-    <t>1003,2003</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>登录{0}天</t>
-  </si>
-  <si>
-    <t>追风剑</t>
-  </si>
-  <si>
-    <t>Bag/Equip/Box_Equip_1_4</t>
-  </si>
-  <si>
-    <t>5000,500,500</t>
-  </si>
-  <si>
-    <t>cd</t>
-  </si>
-  <si>
-    <t>专属</t>
-  </si>
-  <si>
-    <t>疾风弩</t>
-  </si>
-  <si>
-    <t>Bag/Equip/Box_Equip_1_5</t>
-  </si>
-  <si>
-    <t>6000,600,600</t>
   </si>
   <si>
     <t>攻速</t>
@@ -1170,7 +1176,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XEP19"/>
+  <dimension ref="A1:XER19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1182,31 +1188,32 @@
     <col min="8" max="8" width="20" style="2" customWidth="1"/>
     <col min="9" max="9" width="17.25" style="2" customWidth="1"/>
     <col min="10" max="11" width="20.5" style="2" customWidth="1"/>
-    <col min="12" max="12" width="12.4166666666667" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.25" style="2" customWidth="1"/>
-    <col min="14" max="16362" width="9" style="2"/>
-    <col min="16363" max="16384" width="9" style="1"/>
+    <col min="12" max="13" width="15.1666666666667" style="2" customWidth="1"/>
+    <col min="14" max="14" width="12.4166666666667" style="2" customWidth="1"/>
+    <col min="15" max="15" width="14.25" style="2" customWidth="1"/>
+    <col min="16" max="16364" width="9" style="2"/>
+    <col min="16365" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="L2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1236,15 +1243,21 @@
       <c r="K3" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="L3" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="M3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+        <v>11</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -1270,45 +1283,57 @@
       <c r="K4" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="L4" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="M4" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+        <v>11</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+      <c r="O5" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1319,31 +1344,37 @@
         <v>40</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>10000</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1354,31 +1385,37 @@
         <v>100</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+        <v>22</v>
+      </c>
+      <c r="L7" s="1">
+        <v>2</v>
+      </c>
+      <c r="M7" s="1">
+        <v>20000</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1389,31 +1426,37 @@
         <v>10</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+        <v>22</v>
+      </c>
+      <c r="L8" s="1">
+        <v>3</v>
+      </c>
+      <c r="M8" s="1">
+        <v>30000</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
@@ -1430,16 +1473,16 @@
         <v>107</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J9" s="1">
         <v>10</v>
@@ -1447,14 +1490,20 @@
       <c r="K9" s="1">
         <v>1</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+      <c r="L9" s="1">
+        <v>4</v>
+      </c>
+      <c r="M9" s="1">
+        <v>40000</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1471,16 +1520,16 @@
         <v>108</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J10" s="1">
         <v>11</v>
@@ -1488,14 +1537,20 @@
       <c r="K10" s="1">
         <v>1</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+      <c r="L10" s="1">
+        <v>4</v>
+      </c>
+      <c r="M10" s="1">
+        <v>40000</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:15 16365:16372">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1512,16 +1567,16 @@
         <v>300</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J11" s="1">
         <v>21</v>
@@ -1529,22 +1584,28 @@
       <c r="K11" s="1">
         <v>1</v>
       </c>
-      <c r="L11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="XEI11" s="1"/>
-      <c r="XEJ11" s="1"/>
+      <c r="L11" s="1">
+        <v>5</v>
+      </c>
+      <c r="M11" s="1">
+        <v>50000</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="XEK11" s="1"/>
       <c r="XEL11" s="1"/>
       <c r="XEM11" s="1"/>
       <c r="XEN11" s="1"/>
       <c r="XEO11" s="1"/>
       <c r="XEP11" s="1"/>
-    </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+      <c r="XEQ11" s="1"/>
+      <c r="XER11" s="1"/>
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:15 16365:16372">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -1561,16 +1622,16 @@
         <v>36</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J12" s="1">
         <v>22</v>
@@ -1578,22 +1639,28 @@
       <c r="K12" s="1">
         <v>5</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="XEI12" s="1"/>
-      <c r="XEJ12" s="1"/>
+      <c r="L12" s="1">
+        <v>5</v>
+      </c>
+      <c r="M12" s="1">
+        <v>50000</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="XEK12" s="1"/>
       <c r="XEL12" s="1"/>
       <c r="XEM12" s="1"/>
       <c r="XEN12" s="1"/>
       <c r="XEO12" s="1"/>
       <c r="XEP12" s="1"/>
-    </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+      <c r="XEQ12" s="1"/>
+      <c r="XER12" s="1"/>
+    </row>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:15 16365:16372">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -1603,16 +1670,18 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-      <c r="XEI13" s="1"/>
-      <c r="XEJ13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
       <c r="XEK13" s="1"/>
       <c r="XEL13" s="1"/>
       <c r="XEM13" s="1"/>
       <c r="XEN13" s="1"/>
       <c r="XEO13" s="1"/>
       <c r="XEP13" s="1"/>
-    </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+      <c r="XEQ13" s="1"/>
+      <c r="XER13" s="1"/>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:15 16365:16372">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -1622,16 +1691,18 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="XEI14" s="1"/>
-      <c r="XEJ14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
       <c r="XEK14" s="1"/>
       <c r="XEL14" s="1"/>
       <c r="XEM14" s="1"/>
       <c r="XEN14" s="1"/>
       <c r="XEO14" s="1"/>
       <c r="XEP14" s="1"/>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:13 16363:16370">
+      <c r="XEQ14" s="1"/>
+      <c r="XER14" s="1"/>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:15 16365:16372">
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -1641,50 +1712,60 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="XEI15" s="1"/>
-      <c r="XEJ15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
       <c r="XEK15" s="1"/>
       <c r="XEL15" s="1"/>
       <c r="XEM15" s="1"/>
       <c r="XEN15" s="1"/>
       <c r="XEO15" s="1"/>
       <c r="XEP15" s="1"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:13 16363:16370">
+      <c r="XEQ15" s="1"/>
+      <c r="XER15" s="1"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:15 16365:16372">
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-    </row>
-    <row r="17" customHeight="1" spans="6:11">
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+    </row>
+    <row r="17" customHeight="1" spans="6:13">
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
-    </row>
-    <row r="18" customHeight="1" spans="6:11">
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+    </row>
+    <row r="18" customHeight="1" spans="6:13">
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-    </row>
-    <row r="19" customHeight="1" spans="6:11">
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+    </row>
+    <row r="19" customHeight="1" spans="6:13">
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:K3 C4:I4 J4 K4 C5:I5 J5 K5 M3:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3 M3 L4 M4 L5 M5 O3:O5 C3:K5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/WeaponConfig.xlsx
+++ b/Excel/WeaponConfig.xlsx
@@ -124,25 +124,25 @@
     <t>防御</t>
   </si>
   <si>
+    <t>登录{0}天</t>
+  </si>
+  <si>
+    <t>惊鸿剑</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_1</t>
+  </si>
+  <si>
+    <t>2000,200,200</t>
+  </si>
+  <si>
+    <t>1003,2003</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
     <t>看广告{0}个</t>
-  </si>
-  <si>
-    <t>惊鸿剑</t>
-  </si>
-  <si>
-    <t>Bag/Equip/Box_Equip_1_1</t>
-  </si>
-  <si>
-    <t>2000,200,200</t>
-  </si>
-  <si>
-    <t>1003,2003</t>
-  </si>
-  <si>
-    <t>攻击</t>
-  </si>
-  <si>
-    <t>登录{0}天</t>
   </si>
   <si>
     <t>追风剑</t>
@@ -1382,7 +1382,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="1">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>25</v>
@@ -1406,7 +1406,7 @@
         <v>2</v>
       </c>
       <c r="M7" s="1">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>29</v>
@@ -1423,7 +1423,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>31</v>
@@ -1447,7 +1447,7 @@
         <v>3</v>
       </c>
       <c r="M8" s="1">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>35</v>
@@ -1765,7 +1765,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3 M3 L4 M4 L5 M5 O3:O5 C3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O3:O5 C3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/WeaponConfig.xlsx
+++ b/Excel/WeaponConfig.xlsx
@@ -85,7 +85,7 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>归元佩</t>
+    <t>归元链</t>
   </si>
   <si>
     <t>Bag/Equip/Box_Equip_1_3</t>

--- a/Excel/WeaponConfig.xlsx
+++ b/Excel/WeaponConfig.xlsx
@@ -1341,7 +1341,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>17</v>
@@ -1382,7 +1382,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>25</v>

--- a/Excel/WeaponConfig.xlsx
+++ b/Excel/WeaponConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="59">
   <si>
     <t>#</t>
   </si>
@@ -145,31 +145,40 @@
     <t>看广告{0}个</t>
   </si>
   <si>
-    <t>追风剑</t>
-  </si>
-  <si>
-    <t>Bag/Equip/Box_Equip_1_4</t>
+    <t>飞影追魂卷</t>
+  </si>
+  <si>
+    <t>Store/Store5002</t>
   </si>
   <si>
     <t>3000,300,300</t>
   </si>
   <si>
+    <t>1003,10</t>
+  </si>
+  <si>
+    <t>10,2</t>
+  </si>
+  <si>
     <t>cd</t>
   </si>
   <si>
-    <t>专属</t>
-  </si>
-  <si>
-    <t>疾风弩</t>
-  </si>
-  <si>
-    <t>Bag/Equip/Box_Equip_1_5</t>
-  </si>
-  <si>
-    <t>4000,400,400</t>
+    <t>需要道具飞影追魂卷</t>
+  </si>
+  <si>
+    <t>流光逐影印</t>
+  </si>
+  <si>
+    <t>Store/Store5004</t>
+  </si>
+  <si>
+    <t>1003,11</t>
   </si>
   <si>
     <t>攻速</t>
+  </si>
+  <si>
+    <t>需要道具流光逐影印</t>
   </si>
   <si>
     <t>追魂刺</t>
@@ -1457,12 +1466,6 @@
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
-      <c r="A9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1470,7 +1473,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="1">
-        <v>107</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>37</v>
@@ -1484,32 +1487,26 @@
       <c r="I9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="1">
-        <v>10</v>
-      </c>
-      <c r="K9" s="1">
-        <v>1</v>
+      <c r="J9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="L9" s="1">
         <v>4</v>
       </c>
       <c r="M9" s="1">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1517,37 +1514,37 @@
         <v>5</v>
       </c>
       <c r="E10" s="1">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="J10" s="1">
-        <v>11</v>
-      </c>
-      <c r="K10" s="1">
-        <v>1</v>
+        <v>39</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
       </c>
       <c r="M10" s="1">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="1:15 16365:16372">
@@ -1567,16 +1564,16 @@
         <v>300</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J11" s="1">
         <v>21</v>
@@ -1591,10 +1588,10 @@
         <v>50000</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="XEK11" s="1"/>
       <c r="XEL11" s="1"/>
@@ -1622,16 +1619,16 @@
         <v>36</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J12" s="1">
         <v>22</v>
@@ -1646,10 +1643,10 @@
         <v>50000</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="XEK12" s="1"/>
       <c r="XEL12" s="1"/>

--- a/Excel/WeaponConfig.xlsx
+++ b/Excel/WeaponConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="60">
   <si>
     <t>#</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>Sid</t>
+  </si>
+  <si>
+    <t>Type</t>
   </si>
   <si>
     <t>Condtion</t>
@@ -1185,44 +1188,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XER19"/>
+  <dimension ref="A1:XES19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="4" width="9.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.25" style="2" customWidth="1"/>
-    <col min="10" max="11" width="20.5" style="2" customWidth="1"/>
-    <col min="12" max="13" width="15.1666666666667" style="2" customWidth="1"/>
-    <col min="14" max="14" width="12.4166666666667" style="2" customWidth="1"/>
-    <col min="15" max="15" width="14.25" style="2" customWidth="1"/>
-    <col min="16" max="16364" width="9" style="2"/>
-    <col min="16365" max="16384" width="9" style="1"/>
+    <col min="3" max="5" width="9.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.25" style="2" customWidth="1"/>
+    <col min="11" max="12" width="20.5" style="2" customWidth="1"/>
+    <col min="13" max="14" width="15.1666666666667" style="2" customWidth="1"/>
+    <col min="15" max="15" width="12.4166666666667" style="2" customWidth="1"/>
+    <col min="16" max="16" width="14.25" style="2" customWidth="1"/>
+    <col min="17" max="16365" width="9" style="2"/>
+    <col min="16366" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:16 16366:16373">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="N1" s="1" t="s">
+      <c r="J1" s="2"/>
+      <c r="O1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:16 16366:16373">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="N2" s="1" t="s">
+      <c r="J2" s="2"/>
+      <c r="O2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:16 16366:16373">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1258,15 +1261,18 @@
       <c r="M3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="P3" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:16 16366:16373">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -1298,51 +1304,57 @@
       <c r="M4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="P4" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:16 16366:16373">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:16 16366:16373">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1350,15 +1362,15 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
         <v>20</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I6" s="7" t="s">
@@ -1370,20 +1382,23 @@
       <c r="K6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="1">
         <v>1</v>
       </c>
-      <c r="M6" s="1">
+      <c r="N6" s="1">
         <v>10000</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="P6" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:16 16366:16373">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1391,40 +1406,43 @@
         <v>2</v>
       </c>
       <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
         <v>5</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>19</v>
+      <c r="H7" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>28</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="1">
+        <v>29</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" s="1">
         <v>2</v>
       </c>
-      <c r="M7" s="1">
+      <c r="N7" s="1">
         <v>15000</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="P7" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:16 16366:16373">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1432,40 +1450,43 @@
         <v>3</v>
       </c>
       <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
         <v>100</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>19</v>
+      <c r="H8" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>34</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" s="1">
+        <v>35</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="1">
         <v>3</v>
       </c>
-      <c r="M8" s="1">
+      <c r="N8" s="1">
         <v>20000</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="P8" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:16 16366:16373">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1473,19 +1494,19 @@
         <v>4</v>
       </c>
       <c r="E9" s="1">
+        <v>2</v>
+      </c>
+      <c r="F9" s="1">
         <v>1</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>19</v>
+      <c r="H9" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>40</v>
@@ -1493,20 +1514,23 @@
       <c r="K9" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9" s="1">
         <v>4</v>
       </c>
-      <c r="M9" s="1">
+      <c r="N9" s="1">
         <v>25000</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="P9" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:15 16365:16372">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:16 16366:16373">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1514,40 +1538,43 @@
         <v>5</v>
       </c>
       <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>19</v>
+      <c r="H10" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="L10" s="1">
+        <v>47</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M10" s="1">
         <v>4</v>
       </c>
-      <c r="M10" s="1">
+      <c r="N10" s="1">
         <v>25000</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="P10" s="1" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:15 16365:16372">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:16 16366:16373">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1561,39 +1588,41 @@
         <v>6</v>
       </c>
       <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
         <v>300</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H11" s="7" t="s">
-        <v>19</v>
+      <c r="H11" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="J11" s="1">
+        <v>20</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="K11" s="1">
         <v>21</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>1</v>
       </c>
-      <c r="L11" s="1">
+      <c r="M11" s="1">
         <v>5</v>
       </c>
-      <c r="M11" s="1">
+      <c r="N11" s="1">
         <v>50000</v>
       </c>
-      <c r="N11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="O11" s="1" t="s">
+      <c r="O11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="XEK11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="XEL11" s="1"/>
       <c r="XEM11" s="1"/>
       <c r="XEN11" s="1"/>
@@ -1601,8 +1630,9 @@
       <c r="XEP11" s="1"/>
       <c r="XEQ11" s="1"/>
       <c r="XER11" s="1"/>
+      <c r="XES11" s="1"/>
     </row>
-    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:15 16365:16372">
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:16 16366:16373">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -1616,39 +1646,41 @@
         <v>7</v>
       </c>
       <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
         <v>36</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>19</v>
+      <c r="H12" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="J12" s="1">
+        <v>20</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K12" s="1">
         <v>22</v>
-      </c>
-      <c r="K12" s="1">
-        <v>5</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
       </c>
       <c r="M12" s="1">
+        <v>5</v>
+      </c>
+      <c r="N12" s="1">
         <v>50000</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="XEK12" s="1"/>
+      <c r="P12" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="XEL12" s="1"/>
       <c r="XEM12" s="1"/>
       <c r="XEN12" s="1"/>
@@ -1656,20 +1688,21 @@
       <c r="XEP12" s="1"/>
       <c r="XEQ12" s="1"/>
       <c r="XER12" s="1"/>
+      <c r="XES12" s="1"/>
     </row>
-    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:15 16365:16372">
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:16 16366:16373">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
-      <c r="F13" s="4"/>
+      <c r="F13" s="1"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="H13" s="4"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
-      <c r="XEK13" s="1"/>
+      <c r="N13" s="1"/>
       <c r="XEL13" s="1"/>
       <c r="XEM13" s="1"/>
       <c r="XEN13" s="1"/>
@@ -1677,20 +1710,21 @@
       <c r="XEP13" s="1"/>
       <c r="XEQ13" s="1"/>
       <c r="XER13" s="1"/>
+      <c r="XES13" s="1"/>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:15 16365:16372">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:16 16366:16373">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="4"/>
+      <c r="F14" s="1"/>
       <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="H14" s="4"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
-      <c r="XEK14" s="1"/>
+      <c r="N14" s="1"/>
       <c r="XEL14" s="1"/>
       <c r="XEM14" s="1"/>
       <c r="XEN14" s="1"/>
@@ -1698,20 +1732,21 @@
       <c r="XEP14" s="1"/>
       <c r="XEQ14" s="1"/>
       <c r="XER14" s="1"/>
+      <c r="XES14" s="1"/>
     </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:15 16365:16372">
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:16 16366:16373">
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
-      <c r="F15" s="4"/>
+      <c r="F15" s="1"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="H15" s="4"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
-      <c r="XEK15" s="1"/>
+      <c r="N15" s="1"/>
       <c r="XEL15" s="1"/>
       <c r="XEM15" s="1"/>
       <c r="XEN15" s="1"/>
@@ -1719,50 +1754,51 @@
       <c r="XEP15" s="1"/>
       <c r="XEQ15" s="1"/>
       <c r="XER15" s="1"/>
+      <c r="XES15" s="1"/>
     </row>
-    <row r="16" customHeight="1" spans="1:15 16365:16372">
-      <c r="F16" s="4"/>
+    <row r="16" customHeight="1" spans="1:16 16366:16373">
       <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
+      <c r="H16" s="4"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
     </row>
-    <row r="17" customHeight="1" spans="6:13">
-      <c r="F17" s="4"/>
+    <row r="17" customHeight="1" spans="7:14">
       <c r="G17" s="4"/>
-      <c r="H17" s="1"/>
+      <c r="H17" s="4"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
     </row>
-    <row r="18" customHeight="1" spans="6:13">
-      <c r="F18" s="4"/>
+    <row r="18" customHeight="1" spans="7:14">
       <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
+      <c r="H18" s="4"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
     </row>
-    <row r="19" customHeight="1" spans="6:13">
-      <c r="F19" s="4"/>
+    <row r="19" customHeight="1" spans="7:14">
       <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
+      <c r="H19" s="4"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O3:O5 C3:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="P3:P5 C3:N5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/WeaponConfig.xlsx
+++ b/Excel/WeaponConfig.xlsx
@@ -154,13 +154,13 @@
     <t>Store/Store5002</t>
   </si>
   <si>
-    <t>3000,300,300</t>
+    <t>4000,400,400</t>
   </si>
   <si>
     <t>1003,10</t>
   </si>
   <si>
-    <t>10,2</t>
+    <t>15,3</t>
   </si>
   <si>
     <t>cd</t>
@@ -175,7 +175,7 @@
     <t>Store/Store5004</t>
   </si>
   <si>
-    <t>1003,11</t>
+    <t>1002,11</t>
   </si>
   <si>
     <t>攻速</t>

--- a/Excel/WeaponConfig.xlsx
+++ b/Excel/WeaponConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="65">
   <si>
     <t>#</t>
   </si>
@@ -184,34 +184,49 @@
     <t>需要道具流光逐影印</t>
   </si>
   <si>
-    <t>追魂刺</t>
-  </si>
-  <si>
-    <t>Bag/Equip/Box_Equip_1_6</t>
-  </si>
-  <si>
-    <t>7000,700,700</t>
-  </si>
-  <si>
-    <t>暴击</t>
-  </si>
-  <si>
-    <t>技能总等级300级</t>
-  </si>
-  <si>
-    <t>夺命枪</t>
-  </si>
-  <si>
-    <t>Bag/Equip/Box_Equip_1_7</t>
-  </si>
-  <si>
-    <t>8000,800,800</t>
-  </si>
-  <si>
-    <t>爆伤</t>
-  </si>
-  <si>
-    <t>推图第六区域</t>
+    <t>圣战之刃</t>
+  </si>
+  <si>
+    <t>1,2,3,1004</t>
+  </si>
+  <si>
+    <t>3000,300,300,1</t>
+  </si>
+  <si>
+    <t>1007,10004</t>
+  </si>
+  <si>
+    <t>需要珍宝圣战之刃</t>
+  </si>
+  <si>
+    <t>法神之杖</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_2_1</t>
+  </si>
+  <si>
+    <t>1,2,3,1005</t>
+  </si>
+  <si>
+    <t>1008,10005</t>
+  </si>
+  <si>
+    <t>需要珍宝法神之杖</t>
+  </si>
+  <si>
+    <t>道尊之剑</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_3_1</t>
+  </si>
+  <si>
+    <t>1,2,3,1006</t>
+  </si>
+  <si>
+    <t>1009,10006</t>
+  </si>
+  <si>
+    <t>需要珍宝道尊之剑</t>
   </si>
 </sst>
 </file>
@@ -1575,12 +1590,8 @@
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1" spans="1:16 16366:16373">
-      <c r="A11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1591,35 +1602,33 @@
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>300</v>
-      </c>
-      <c r="G11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>20</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="K11" s="1">
-        <v>21</v>
-      </c>
-      <c r="L11" s="1">
-        <v>1</v>
+      <c r="K11" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="M11" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N11" s="1">
-        <v>50000</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>53</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="O11" s="2"/>
       <c r="P11" s="1" t="s">
         <v>54</v>
       </c>
@@ -1633,12 +1642,8 @@
       <c r="XES11" s="1"/>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="1:16 16366:16373">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>0</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1649,36 +1654,34 @@
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>36</v>
-      </c>
-      <c r="G12" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>55</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>56</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="K12" s="1">
-        <v>22</v>
-      </c>
-      <c r="L12" s="1">
-        <v>5</v>
+        <v>52</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="M12" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N12" s="1">
-        <v>50000</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="P12" s="2" t="s">
+        <v>20000</v>
+      </c>
+      <c r="O12" s="2"/>
+      <c r="P12" s="1" t="s">
         <v>59</v>
       </c>
       <c r="XEL12" s="1"/>
@@ -1691,18 +1694,45 @@
       <c r="XES12" s="1"/>
     </row>
     <row r="13" s="2" customFormat="1" customHeight="1" spans="1:16 16366:16373">
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1">
+        <v>8</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M13" s="1">
+        <v>3</v>
+      </c>
+      <c r="N13" s="1">
+        <v>20000</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>64</v>
+      </c>
       <c r="XEL13" s="1"/>
       <c r="XEM13" s="1"/>
       <c r="XEN13" s="1"/>

--- a/Excel/WeaponConfig.xlsx
+++ b/Excel/WeaponConfig.xlsx
@@ -157,10 +157,10 @@
     <t>4000,400,400</t>
   </si>
   <si>
-    <t>1003,10</t>
-  </si>
-  <si>
-    <t>15,3</t>
+    <t>10003,10</t>
+  </si>
+  <si>
+    <t>2,3</t>
   </si>
   <si>
     <t>cd</t>
@@ -175,7 +175,7 @@
     <t>Store/Store5004</t>
   </si>
   <si>
-    <t>1002,11</t>
+    <t>10002,11</t>
   </si>
   <si>
     <t>攻速</t>

--- a/Excel/WeaponConfig.xlsx
+++ b/Excel/WeaponConfig.xlsx
@@ -175,7 +175,7 @@
     <t>Store/Store5004</t>
   </si>
   <si>
-    <t>10002,11</t>
+    <t>10003,11</t>
   </si>
   <si>
     <t>攻速</t>
